--- a/Expiry Tracker System.xlsx
+++ b/Expiry Tracker System.xlsx
@@ -968,9 +968,6 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -980,26 +977,15 @@
     <xf numFmtId="15" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="2">
     <dxf>
       <fill>
         <patternFill>
@@ -1306,15 +1292,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="22" t="s">
         <v>113</v>
       </c>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
     </row>
     <row r="3" spans="2:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
@@ -1361,7 +1347,7 @@
       </c>
       <c r="H4" s="16">
         <f t="shared" ref="H4:H31" ca="1" si="0">IF(F4&lt;&gt;"", F4-TODAY(), "")</f>
-        <v>163</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1386,7 +1372,7 @@
       </c>
       <c r="H5" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>155</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1411,7 +1397,7 @@
       </c>
       <c r="H6" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>-22</v>
+        <v>-58</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1436,7 +1422,7 @@
       </c>
       <c r="H7" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>117</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1461,7 +1447,7 @@
       </c>
       <c r="H8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>99</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1486,7 +1472,7 @@
       </c>
       <c r="H9" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>853</v>
+        <v>817</v>
       </c>
       <c r="J9" t="s">
         <v>174</v>
@@ -1514,7 +1500,7 @@
       </c>
       <c r="H10" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1117</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1539,7 +1525,7 @@
       </c>
       <c r="H11" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>-19</v>
+        <v>-55</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1560,11 +1546,11 @@
       </c>
       <c r="G12" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Expiring Soon</v>
+        <v>Expired</v>
       </c>
       <c r="H12" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1585,11 +1571,11 @@
       </c>
       <c r="G13" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Expiring Soon</v>
+        <v>Expired</v>
       </c>
       <c r="H13" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1610,11 +1596,11 @@
       </c>
       <c r="G14" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Expiring Soon</v>
+        <v>Expired</v>
       </c>
       <c r="H14" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>-34</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1639,7 +1625,7 @@
       </c>
       <c r="H15" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1301</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1664,7 +1650,7 @@
       </c>
       <c r="H16" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1169</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1689,7 +1675,7 @@
       </c>
       <c r="H17" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1057</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1714,7 +1700,7 @@
       </c>
       <c r="H18" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>520</v>
+        <v>484</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1739,7 +1725,7 @@
       </c>
       <c r="H19" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>520</v>
+        <v>484</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1760,11 +1746,11 @@
       </c>
       <c r="G20" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Valid</v>
+        <v>Expiring Soon</v>
       </c>
       <c r="H20" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>38</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1789,7 +1775,7 @@
       </c>
       <c r="H21" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>355</v>
+        <v>319</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1839,7 +1825,7 @@
       </c>
       <c r="H23" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>348</v>
+        <v>312</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1864,7 +1850,7 @@
       </c>
       <c r="H24" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>-210</v>
+        <v>-246</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1887,7 +1873,7 @@
       </c>
       <c r="H25" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>519</v>
+        <v>483</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1912,7 +1898,7 @@
       </c>
       <c r="H26" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1250</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1935,7 +1921,7 @@
       </c>
       <c r="H27" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>-210</v>
+        <v>-246</v>
       </c>
     </row>
     <row r="28" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1958,7 +1944,7 @@
       </c>
       <c r="H28" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>519</v>
+        <v>483</v>
       </c>
     </row>
     <row r="29" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1983,7 +1969,7 @@
       </c>
       <c r="H29" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>885</v>
+        <v>849</v>
       </c>
     </row>
     <row r="30" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -2008,7 +1994,7 @@
       </c>
       <c r="H30" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1251</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="31" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -2037,28 +2023,28 @@
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="20">
+      <c r="B32" s="19">
         <v>31</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="20" t="s">
         <v>182</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="21">
         <v>45839</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="21">
         <v>46203</v>
       </c>
-      <c r="G32" s="21" t="str">
+      <c r="G32" s="20" t="str">
         <f t="shared" ref="G32" ca="1" si="2">IF(H32&lt;0, "Expired", IF(H32&lt;=30, "Expiring Soon", "Valid"))</f>
         <v>Valid</v>
       </c>
-      <c r="H32" s="21">
+      <c r="H32" s="20">
         <f t="shared" ref="H32" ca="1" si="3">IF(F32&lt;&gt;"", F32-TODAY(), "")</f>
-        <v>336</v>
+        <v>300</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
@@ -2094,12 +2080,12 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4:H31">
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H4">
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThanOrEqual">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThanOrEqual">
       <formula>30</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Expiry Tracker System.xlsx
+++ b/Expiry Tracker System.xlsx
@@ -17,7 +17,7 @@
     <sheet name="TPA List" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Expiry tracker'!$B$2:$H$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Expiry tracker'!$B$2:$H$27</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="175">
   <si>
     <t>Description</t>
   </si>
@@ -493,18 +493,6 @@
     <t>MOU  Elite</t>
   </si>
   <si>
-    <t>MOU  Soni Hospital</t>
-  </si>
-  <si>
-    <t>MOU  K.P Diagnosis</t>
-  </si>
-  <si>
-    <t>MOU  ICU</t>
-  </si>
-  <si>
-    <t>MOU  Dhobi</t>
-  </si>
-  <si>
     <t>Allenger C-ARM</t>
   </si>
   <si>
@@ -535,9 +523,6 @@
     <t>Hospital Insurance</t>
   </si>
   <si>
-    <t>Policy no. OG-25-1412-4056-00000905</t>
-  </si>
-  <si>
     <t>Rohini Id</t>
   </si>
   <si>
@@ -751,24 +736,12 @@
     <t xml:space="preserve">License No. RAJ-2520 </t>
   </si>
   <si>
-    <t xml:space="preserve"> Sony Hospital </t>
-  </si>
-  <si>
     <t>Elite imagine center</t>
   </si>
   <si>
     <t>Shree Vinayk  Ambulance Service</t>
   </si>
   <si>
-    <t xml:space="preserve">K.P Dignosi center </t>
-  </si>
-  <si>
-    <t>ICU services</t>
-  </si>
-  <si>
-    <t>K.P Lundary services</t>
-  </si>
-  <si>
     <t>C-ARM Licwnce No - Rj- 115957-RF-XR-001</t>
   </si>
   <si>
@@ -806,6 +779,9 @@
   </si>
   <si>
     <t>Doctor payment</t>
+  </si>
+  <si>
+    <t>Policy no. OG-26-1412-4056-00000443</t>
   </si>
 </sst>
 </file>
@@ -1279,7 +1255,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:J34"/>
+  <dimension ref="B2:J30"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="4" bestFit="1" customWidth="1"/>
@@ -1293,7 +1269,7 @@
   <sheetData>
     <row r="2" spans="2:10" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="22" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C2" s="22"/>
       <c r="D2" s="22"/>
@@ -1304,7 +1280,7 @@
     </row>
     <row r="3" spans="2:10" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="13" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="C3" s="13" t="s">
         <v>3</v>
@@ -1313,10 +1289,10 @@
         <v>0</v>
       </c>
       <c r="E3" s="13" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="G3" s="14" t="s">
         <v>1</v>
@@ -1333,7 +1309,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="E4" s="17">
         <v>45300</v>
@@ -1346,8 +1322,8 @@
         <v>Valid</v>
       </c>
       <c r="H4" s="16">
-        <f t="shared" ref="H4:H31" ca="1" si="0">IF(F4&lt;&gt;"", F4-TODAY(), "")</f>
-        <v>127</v>
+        <f t="shared" ref="H4:H27" ca="1" si="0">IF(F4&lt;&gt;"", F4-TODAY(), "")</f>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1358,7 +1334,7 @@
         <v>5</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="E5" s="17">
         <v>45658</v>
@@ -1372,7 +1348,7 @@
       </c>
       <c r="H5" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>119</v>
+        <v>97</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1383,21 +1359,21 @@
         <v>6</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E6" s="17">
-        <v>45481</v>
+        <v>45919</v>
       </c>
       <c r="F6" s="18">
-        <v>45845</v>
+        <v>46283</v>
       </c>
       <c r="G6" s="16" t="str">
         <f ca="1">IF(H6&lt;0, "Expired", IF(H6&lt;=30, "Expiring Soon", "Valid"))</f>
-        <v>Expired</v>
+        <v>Valid</v>
       </c>
       <c r="H6" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>-58</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1405,10 +1381,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="16" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="E7" s="17">
         <v>45620</v>
@@ -1422,7 +1398,7 @@
       </c>
       <c r="H7" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>81</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1430,10 +1406,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="16" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="E8" s="17">
         <v>44141</v>
@@ -1442,12 +1418,12 @@
         <v>45966</v>
       </c>
       <c r="G8" s="16" t="str">
-        <f t="shared" ref="G8:G31" ca="1" si="1">IF(H8&lt;0, "Expired", IF(H8&lt;=30, "Expiring Soon", "Valid"))</f>
+        <f t="shared" ref="G8:G27" ca="1" si="1">IF(H8&lt;0, "Expired", IF(H8&lt;=30, "Expiring Soon", "Valid"))</f>
         <v>Valid</v>
       </c>
       <c r="H8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>63</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1458,7 +1434,7 @@
         <v>76</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>166</v>
+        <v>160</v>
       </c>
       <c r="E9" s="17">
         <v>45626</v>
@@ -1472,10 +1448,10 @@
       </c>
       <c r="H9" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>817</v>
+        <v>795</v>
       </c>
       <c r="J9" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1486,7 +1462,7 @@
         <v>77</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="E10" s="17">
         <v>45157</v>
@@ -1500,124 +1476,124 @@
       </c>
       <c r="H10" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1081</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B11" s="15">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C11" s="16" t="s">
         <v>78</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="E11" s="17">
-        <v>45139</v>
+        <v>45341</v>
       </c>
       <c r="F11" s="17">
-        <v>45848</v>
+        <v>47168</v>
       </c>
       <c r="G11" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Expired</v>
+        <v>Valid</v>
       </c>
       <c r="H11" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>-55</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B12" s="15">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="C12" s="16" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>167</v>
+        <v>81</v>
       </c>
       <c r="E12" s="17">
-        <v>45139</v>
+        <v>45210</v>
       </c>
       <c r="F12" s="17">
-        <v>45869</v>
+        <v>47036</v>
       </c>
       <c r="G12" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Expired</v>
+        <v>Valid</v>
       </c>
       <c r="H12" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>-34</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B13" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="C13" s="16" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>168</v>
+        <v>82</v>
       </c>
       <c r="E13" s="17">
-        <v>45139</v>
+        <v>45098</v>
       </c>
       <c r="F13" s="17">
-        <v>45869</v>
+        <v>46924</v>
       </c>
       <c r="G13" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Expired</v>
+        <v>Valid</v>
       </c>
       <c r="H13" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>-34</v>
+        <v>999</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B14" s="15">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C14" s="16" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E14" s="17">
-        <v>45139</v>
+        <v>45126</v>
       </c>
       <c r="F14" s="17">
-        <v>45869</v>
+        <v>46387</v>
       </c>
       <c r="G14" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Expired</v>
+        <v>Valid</v>
       </c>
       <c r="H14" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>-34</v>
+        <v>462</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B15" s="15">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="C15" s="16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E15" s="17">
-        <v>45341</v>
+        <v>45126</v>
       </c>
       <c r="F15" s="17">
-        <v>47168</v>
+        <v>46387</v>
       </c>
       <c r="G15" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1625,24 +1601,24 @@
       </c>
       <c r="H15" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1265</v>
+        <v>462</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B16" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C16" s="16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>85</v>
+        <v>174</v>
       </c>
       <c r="E16" s="17">
-        <v>45210</v>
+        <v>45906</v>
       </c>
       <c r="F16" s="17">
-        <v>47036</v>
+        <v>46270</v>
       </c>
       <c r="G16" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1650,24 +1626,24 @@
       </c>
       <c r="H16" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1133</v>
+        <v>345</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B17" s="15">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C17" s="16" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="E17" s="17">
-        <v>45098</v>
+        <v>45127</v>
       </c>
       <c r="F17" s="17">
-        <v>46924</v>
+        <v>46222</v>
       </c>
       <c r="G17" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1675,49 +1651,49 @@
       </c>
       <c r="H17" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1021</v>
+        <v>297</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B18" s="15">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C18" s="16" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D18" s="16" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="E18" s="17">
-        <v>45126</v>
-      </c>
-      <c r="F18" s="17">
-        <v>46387</v>
-      </c>
-      <c r="G18" s="16" t="str">
+        <v>45061</v>
+      </c>
+      <c r="F18" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="G18" s="16" t="e">
         <f t="shared" ca="1" si="1"/>
-        <v>Valid</v>
-      </c>
-      <c r="H18" s="16">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H18" s="16" t="e">
         <f t="shared" ca="1" si="0"/>
-        <v>484</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="19" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B19" s="15">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="C19" s="16" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>177</v>
+        <v>162</v>
       </c>
       <c r="E19" s="17">
-        <v>45126</v>
+        <v>45851</v>
       </c>
       <c r="F19" s="17">
-        <v>46387</v>
+        <v>46215</v>
       </c>
       <c r="G19" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1725,49 +1701,47 @@
       </c>
       <c r="H19" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>484</v>
+        <v>290</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B20" s="15">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="C20" s="16" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E20" s="17">
-        <v>45541</v>
+        <v>43831</v>
       </c>
       <c r="F20" s="17">
-        <v>45905</v>
+        <v>45657</v>
       </c>
       <c r="G20" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Expiring Soon</v>
+        <v>Expired</v>
       </c>
       <c r="H20" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>2</v>
+        <v>-268</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B21" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C21" s="16" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>94</v>
-      </c>
-      <c r="E21" s="17">
-        <v>45127</v>
-      </c>
+        <v>100</v>
+      </c>
+      <c r="E21" s="16"/>
       <c r="F21" s="17">
-        <v>46222</v>
+        <v>46386</v>
       </c>
       <c r="G21" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1775,97 +1749,95 @@
       </c>
       <c r="H21" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>319</v>
+        <v>461</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B22" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C22" s="16" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>172</v>
+        <v>101</v>
       </c>
       <c r="E22" s="17">
-        <v>45061</v>
-      </c>
-      <c r="F22" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="G22" s="16" t="e">
+        <v>45345</v>
+      </c>
+      <c r="F22" s="17">
+        <v>47117</v>
+      </c>
+      <c r="G22" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="H22" s="16" t="e">
+        <v>Valid</v>
+      </c>
+      <c r="H22" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>#VALUE!</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B23" s="15">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="C23" s="16" t="s">
-        <v>97</v>
+        <v>154</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>171</v>
-      </c>
-      <c r="E23" s="17">
-        <v>45851</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="E23" s="16"/>
       <c r="F23" s="17">
-        <v>46215</v>
+        <v>45657</v>
       </c>
       <c r="G23" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Valid</v>
+        <v>Expired</v>
       </c>
       <c r="H23" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>312</v>
+        <v>-268</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B24" s="15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C24" s="16" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="E24" s="17">
-        <v>43831</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="E24" s="16"/>
       <c r="F24" s="17">
-        <v>45657</v>
+        <v>46386</v>
       </c>
       <c r="G24" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
-        <v>Expired</v>
+        <v>Valid</v>
       </c>
       <c r="H24" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>-246</v>
+        <v>461</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B25" s="15">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="C25" s="16" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="D25" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="16"/>
+        <v>104</v>
+      </c>
+      <c r="E25" s="17">
+        <v>44927</v>
+      </c>
       <c r="F25" s="17">
-        <v>46386</v>
+        <v>46752</v>
       </c>
       <c r="G25" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1873,24 +1845,24 @@
       </c>
       <c r="H25" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>483</v>
+        <v>827</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B26" s="15">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D26" s="16" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="E26" s="17">
-        <v>45345</v>
+        <v>45292</v>
       </c>
       <c r="F26" s="17">
-        <v>47117</v>
+        <v>47118</v>
       </c>
       <c r="G26" s="16" t="str">
         <f t="shared" ca="1" si="1"/>
@@ -1898,172 +1870,76 @@
       </c>
       <c r="H26" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1214</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B27" s="15">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="C27" s="16" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="D27" s="16" t="s">
+        <v>106</v>
+      </c>
+      <c r="E27" s="16" t="s">
         <v>107</v>
       </c>
-      <c r="E27" s="16"/>
-      <c r="F27" s="17">
-        <v>45657</v>
-      </c>
-      <c r="G27" s="16" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Expired</v>
-      </c>
-      <c r="H27" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>-246</v>
-      </c>
-    </row>
-    <row r="28" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B28" s="15">
-        <v>27</v>
-      </c>
-      <c r="C28" s="16" t="s">
-        <v>102</v>
-      </c>
-      <c r="D28" s="16" t="s">
-        <v>108</v>
-      </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="17">
-        <v>46386</v>
-      </c>
-      <c r="G28" s="16" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Valid</v>
-      </c>
-      <c r="H28" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>483</v>
-      </c>
-    </row>
-    <row r="29" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B29" s="15">
-        <v>28</v>
-      </c>
-      <c r="C29" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="D29" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="E29" s="17">
-        <v>44927</v>
-      </c>
-      <c r="F29" s="17">
-        <v>46752</v>
-      </c>
-      <c r="G29" s="16" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Valid</v>
-      </c>
-      <c r="H29" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>849</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B30" s="15">
-        <v>29</v>
-      </c>
-      <c r="C30" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="D30" s="16" t="s">
-        <v>110</v>
-      </c>
-      <c r="E30" s="17">
-        <v>45292</v>
-      </c>
-      <c r="F30" s="17">
-        <v>47118</v>
-      </c>
-      <c r="G30" s="16" t="str">
-        <f t="shared" ca="1" si="1"/>
-        <v>Valid</v>
-      </c>
-      <c r="H30" s="16">
-        <f t="shared" ca="1" si="0"/>
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="31" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="B31" s="15">
-        <v>30</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>175</v>
-      </c>
-      <c r="D31" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="E31" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>112</v>
-      </c>
-      <c r="G31" s="16" t="e">
+      <c r="F27" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="G27" s="16" t="e">
         <f t="shared" ca="1" si="1"/>
         <v>#VALUE!</v>
       </c>
-      <c r="H31" s="16" t="e">
+      <c r="H27" s="16" t="e">
         <f t="shared" ca="1" si="0"/>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="19">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="19">
         <v>31</v>
       </c>
-      <c r="C32" s="20" t="s">
-        <v>182</v>
-      </c>
-      <c r="D32" s="20" t="s">
-        <v>181</v>
-      </c>
-      <c r="E32" s="21">
+      <c r="C28" s="20" t="s">
+        <v>173</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>172</v>
+      </c>
+      <c r="E28" s="21">
         <v>45839</v>
       </c>
-      <c r="F32" s="21">
+      <c r="F28" s="21">
         <v>46203</v>
       </c>
-      <c r="G32" s="20" t="str">
-        <f t="shared" ref="G32" ca="1" si="2">IF(H32&lt;0, "Expired", IF(H32&lt;=30, "Expiring Soon", "Valid"))</f>
+      <c r="G28" s="20" t="str">
+        <f t="shared" ref="G28" ca="1" si="2">IF(H28&lt;0, "Expired", IF(H28&lt;=30, "Expiring Soon", "Valid"))</f>
         <v>Valid</v>
       </c>
-      <c r="H32" s="20">
-        <f t="shared" ref="H32" ca="1" si="3">IF(F32&lt;&gt;"", F32-TODAY(), "")</f>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="2"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-    </row>
-    <row r="34" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C34" s="12"/>
+      <c r="H28" s="20">
+        <f t="shared" ref="H28" ca="1" si="3">IF(F28&lt;&gt;"", F28-TODAY(), "")</f>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="29" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="2"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+    </row>
+    <row r="30" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C30" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:H2"/>
   </mergeCells>
-  <conditionalFormatting sqref="G4:G6">
+  <conditionalFormatting sqref="G4:G27">
     <cfRule type="cellIs" priority="8" operator="equal">
       <formula>#REF!</formula>
     </cfRule>
@@ -2071,15 +1947,7 @@
       <formula>"""Expired"""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G7:G31">
-    <cfRule type="cellIs" priority="4" operator="equal">
-      <formula>#REF!</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal">
-      <formula>"""Expired"""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H4:H31">
+  <conditionalFormatting sqref="H4:H27">
     <cfRule type="cellIs" dxfId="1" priority="2" operator="lessThan">
       <formula>1</formula>
     </cfRule>
@@ -2090,7 +1958,7 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="97" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="98" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2418,22 +2286,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="B1" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D1" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="E1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="F1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -2441,16 +2309,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C2" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="E2" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -2458,16 +2326,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="C3" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -2475,16 +2343,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C4" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -2492,16 +2360,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E5" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -2509,16 +2377,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="C6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -2526,16 +2394,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C7" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="E7" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -2543,16 +2411,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="C8" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -2560,16 +2428,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="C9" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E9" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -2577,16 +2445,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C10" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="E10" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -2594,13 +2462,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="E11" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -2608,13 +2476,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="E12" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -2622,13 +2490,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="E13" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -2636,13 +2504,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="E14" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">

--- a/Expiry Tracker System.xlsx
+++ b/Expiry Tracker System.xlsx
@@ -1323,7 +1323,7 @@
       </c>
       <c r="H4" s="16">
         <f t="shared" ref="H4:H27" ca="1" si="0">IF(F4&lt;&gt;"", F4-TODAY(), "")</f>
-        <v>105</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H5" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>97</v>
+        <v>83</v>
       </c>
     </row>
     <row r="6" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="H6" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>358</v>
+        <v>344</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1398,7 +1398,7 @@
       </c>
       <c r="H7" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1419,11 +1419,11 @@
       </c>
       <c r="G8" s="16" t="str">
         <f t="shared" ref="G8:G27" ca="1" si="1">IF(H8&lt;0, "Expired", IF(H8&lt;=30, "Expiring Soon", "Valid"))</f>
-        <v>Valid</v>
+        <v>Expiring Soon</v>
       </c>
       <c r="H8" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>41</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="H9" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>795</v>
+        <v>781</v>
       </c>
       <c r="J9" t="s">
         <v>165</v>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="H10" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1059</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="11" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="H11" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1243</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1526,7 +1526,7 @@
       </c>
       <c r="H12" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1111</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="H13" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>999</v>
+        <v>985</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="H14" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>462</v>
+        <v>448</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="H15" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>462</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16" spans="2:10" ht="15.75" x14ac:dyDescent="0.25">
@@ -1626,7 +1626,7 @@
       </c>
       <c r="H16" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>345</v>
+        <v>331</v>
       </c>
     </row>
     <row r="17" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="H17" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>297</v>
+        <v>283</v>
       </c>
     </row>
     <row r="18" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="H19" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>290</v>
+        <v>276</v>
       </c>
     </row>
     <row r="20" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="H20" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>-268</v>
+        <v>-282</v>
       </c>
     </row>
     <row r="21" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1749,7 +1749,7 @@
       </c>
       <c r="H21" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>447</v>
       </c>
     </row>
     <row r="22" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="H22" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1192</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="23" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1797,7 +1797,7 @@
       </c>
       <c r="H23" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>-268</v>
+        <v>-282</v>
       </c>
     </row>
     <row r="24" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H24" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>461</v>
+        <v>447</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="H25" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>827</v>
+        <v>813</v>
       </c>
     </row>
     <row r="26" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1870,7 +1870,7 @@
       </c>
       <c r="H26" s="16">
         <f t="shared" ca="1" si="0"/>
-        <v>1193</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="27" spans="2:8" ht="15.75" x14ac:dyDescent="0.25">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="H28" s="20">
         <f t="shared" ref="H28" ca="1" si="3">IF(F28&lt;&gt;"", F28-TODAY(), "")</f>
-        <v>278</v>
+        <v>264</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.25">
